--- a/Team-Data/2014-15/2-20-2014-15.xlsx
+++ b/Team-Data/2014-15/2-20-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
         <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.782</v>
+        <v>0.796</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468</v>
+        <v>0.471</v>
       </c>
       <c r="L2" t="n">
         <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.385</v>
+        <v>0.389</v>
       </c>
       <c r="O2" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P2" t="n">
         <v>22.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>32.6</v>
       </c>
       <c r="T2" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W2" t="n">
         <v>8.800000000000001</v>
@@ -727,19 +794,19 @@
         <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>103</v>
+        <v>103.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -754,22 +821,22 @@
         <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ2" t="n">
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
         <v>12</v>
@@ -778,7 +845,7 @@
         <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
@@ -802,7 +869,7 @@
         <v>16</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -861,46 +928,46 @@
         <v>39.1</v>
       </c>
       <c r="J3" t="n">
-        <v>87.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M3" t="n">
         <v>23.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
         <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.75</v>
+        <v>0.755</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U3" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="V3" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X3" t="n">
         <v>3.9</v>
@@ -912,25 +979,25 @@
         <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AB3" t="n">
         <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
       </c>
       <c r="AF3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG3" t="n">
         <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
       </c>
       <c r="AH3" t="n">
         <v>14</v>
@@ -948,7 +1015,7 @@
         <v>13</v>
       </c>
       <c r="AM3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="n">
         <v>24</v>
@@ -960,34 +1027,34 @@
         <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -996,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.415</v>
+        <v>0.404</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1055,16 +1122,16 @@
         <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.324</v>
+        <v>0.321</v>
       </c>
       <c r="O4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P4" t="n">
         <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R4" t="n">
         <v>9.9</v>
@@ -1073,13 +1140,13 @@
         <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1097,16 +1164,16 @@
         <v>19.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
@@ -1139,10 +1206,10 @@
         <v>24</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1154,10 +1221,10 @@
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1175,7 +1242,7 @@
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1321,7 +1388,7 @@
         <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
@@ -1330,10 +1397,10 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1348,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
         <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.618</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,7 +1474,7 @@
         <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.444</v>
@@ -1416,7 +1483,7 @@
         <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N6" t="n">
         <v>0.359</v>
@@ -1425,28 +1492,28 @@
         <v>20.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
         <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T6" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X6" t="n">
         <v>6.3</v>
@@ -1455,25 +1522,25 @@
         <v>5.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA6" t="n">
         <v>21.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>102.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
         <v>9</v>
@@ -1485,7 +1552,7 @@
         <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1506,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1518,7 +1585,7 @@
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1533,13 +1600,13 @@
         <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="n">
         <v>18.3</v>
@@ -1616,13 +1683,13 @@
         <v>11.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T7" t="n">
         <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.9</v>
@@ -1634,34 +1701,34 @@
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
         <v>18.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.6</v>
+        <v>102.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1685,13 +1752,13 @@
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>22</v>
@@ -1715,16 +1782,16 @@
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1756,22 +1823,22 @@
         <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.661</v>
+        <v>0.643</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J8" t="n">
-        <v>86.3</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
         <v>0.463</v>
@@ -1780,7 +1847,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N8" t="n">
         <v>0.357</v>
@@ -1792,43 +1859,43 @@
         <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>13</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,10 +1928,10 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
@@ -1873,13 +1940,13 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT8" t="n">
         <v>20</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -1935,49 +2002,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L9" t="n">
         <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R9" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>32.9</v>
@@ -1992,55 +2059,55 @@
         <v>14.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y9" t="n">
         <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA9" t="n">
         <v>20.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.3</v>
+        <v>100.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>23</v>
       </c>
       <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
         <v>16</v>
       </c>
-      <c r="AI9" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN9" t="n">
         <v>28</v>
@@ -2049,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2067,13 +2134,13 @@
         <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2082,13 +2149,13 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2138,7 +2205,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
         <v>8.6</v>
@@ -2147,16 +2214,16 @@
         <v>25.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O10" t="n">
         <v>16.4</v>
       </c>
       <c r="P10" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.708</v>
+        <v>0.712</v>
       </c>
       <c r="R10" t="n">
         <v>12.8</v>
@@ -2168,43 +2235,43 @@
         <v>45.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB10" t="n">
         <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
         <v>20</v>
@@ -2225,7 +2292,7 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>22</v>
@@ -2246,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>13</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>18</v>
@@ -2264,13 +2331,13 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.827</v>
+        <v>0.824</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,43 +2384,43 @@
         <v>41.8</v>
       </c>
       <c r="J11" t="n">
-        <v>86.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="K11" t="n">
         <v>0.481</v>
       </c>
       <c r="L11" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M11" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.384</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S11" t="n">
         <v>34.7</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U11" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W11" t="n">
         <v>9.4</v>
@@ -2362,7 +2429,7 @@
         <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z11" t="n">
         <v>19.8</v>
@@ -2377,10 +2444,10 @@
         <v>10.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -2407,22 +2474,22 @@
         <v>3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>5</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -2484,22 +2551,22 @@
         <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.66</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2508,16 +2575,16 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0.718</v>
@@ -2532,43 +2599,43 @@
         <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
@@ -2577,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,7 +2686,7 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2696,13 +2763,13 @@
         <v>0.333</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P13" t="n">
         <v>21.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R13" t="n">
         <v>10.6</v>
@@ -2720,13 +2787,13 @@
         <v>14.4</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X13" t="n">
         <v>4.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z13" t="n">
         <v>20.8</v>
@@ -2735,25 +2802,25 @@
         <v>20.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2762,7 +2829,7 @@
         <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2777,22 +2844,22 @@
         <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
         <v>17</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>6</v>
       </c>
       <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -2953,7 +3020,7 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2989,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3042,46 +3109,46 @@
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L15" t="n">
         <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.9</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.2</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>23</v>
@@ -3135,7 +3202,7 @@
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
@@ -3144,16 +3211,16 @@
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS15" t="n">
         <v>20</v>
       </c>
-      <c r="AR15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>17</v>
-      </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>22</v>
@@ -3162,22 +3229,22 @@
         <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK16" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3329,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
@@ -3359,7 +3426,7 @@
         <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
         <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>0.434</v>
+        <v>0.423</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
@@ -3409,7 +3476,7 @@
         <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.455</v>
@@ -3421,13 +3488,13 @@
         <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0.742</v>
@@ -3436,16 +3503,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="U17" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
         <v>8</v>
@@ -3454,22 +3521,22 @@
         <v>4.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.3</v>
+        <v>-3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
         <v>20</v>
@@ -3499,13 +3566,13 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>22</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV17" t="n">
         <v>19</v>
@@ -3532,19 +3599,19 @@
         <v>24</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3573,31 +3640,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
         <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J18" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
         <v>18.9</v>
@@ -3612,31 +3679,31 @@
         <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R18" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
         <v>23.7</v>
       </c>
       <c r="V18" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z18" t="n">
         <v>22.3</v>
@@ -3645,13 +3712,13 @@
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3666,7 +3733,7 @@
         <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
@@ -3690,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3711,10 +3778,10 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
@@ -3723,10 +3790,10 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>0.222</v>
+        <v>0.208</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J19" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K19" t="n">
         <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M19" t="n">
         <v>14.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R19" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T19" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U19" t="n">
         <v>22.1</v>
@@ -3818,37 +3885,37 @@
         <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.4</v>
+        <v>-8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>11</v>
@@ -3869,16 +3936,16 @@
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT19" t="n">
         <v>26</v>
@@ -3896,13 +3963,13 @@
         <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -3940,22 +4007,22 @@
         <v>53</v>
       </c>
       <c r="E20" t="n">
+        <v>27</v>
+      </c>
+      <c r="F20" t="n">
         <v>26</v>
       </c>
-      <c r="F20" t="n">
-        <v>27</v>
-      </c>
       <c r="G20" t="n">
-        <v>0.491</v>
+        <v>0.509</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.453</v>
@@ -3967,25 +4034,25 @@
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
@@ -3994,28 +4061,28 @@
         <v>13.1</v>
       </c>
       <c r="W20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
@@ -4030,10 +4097,10 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>13</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>16</v>
       </c>
       <c r="AK20" t="n">
         <v>14</v>
@@ -4054,34 +4121,34 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4158,22 +4225,22 @@
         <v>17.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T21" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U21" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W21" t="n">
         <v>7.2</v>
@@ -4185,19 +4252,19 @@
         <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA21" t="n">
         <v>18.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8</v>
+        <v>-7.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4218,10 +4285,10 @@
         <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM21" t="n">
         <v>20</v>
@@ -4236,22 +4303,22 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>14</v>
@@ -4391,7 +4458,7 @@
         <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>14</v>
@@ -4400,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
@@ -4418,13 +4485,13 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -4433,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
@@ -4448,13 +4515,13 @@
         <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -4486,79 +4553,79 @@
         <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.321</v>
+        <v>0.304</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="P23" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4591,7 +4658,7 @@
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,25 +4682,25 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="J24" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
         <v>0.41</v>
@@ -4701,7 +4768,7 @@
         <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q24" t="n">
         <v>0.6830000000000001</v>
@@ -4710,10 +4777,10 @@
         <v>11.4</v>
       </c>
       <c r="S24" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U24" t="n">
         <v>20.3</v>
@@ -4725,10 +4792,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21.2</v>
@@ -4737,13 +4804,13 @@
         <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,25 +4843,25 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -4847,19 +4914,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>0.527</v>
+        <v>0.537</v>
       </c>
       <c r="H25" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
         <v>39.8</v>
@@ -4868,37 +4935,37 @@
         <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M25" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O25" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P25" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
         <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
         <v>14.9</v>
@@ -4910,31 +4977,31 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>11</v>
@@ -4946,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>7</v>
@@ -4955,37 +5022,37 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.679</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="J26" t="n">
-        <v>86</v>
+        <v>86.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O26" t="n">
         <v>15.9</v>
@@ -5068,19 +5135,19 @@
         <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="R26" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="T26" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V26" t="n">
         <v>13.8</v>
@@ -5095,28 +5162,28 @@
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA26" t="n">
         <v>19.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.1</v>
+        <v>102.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
         <v>8</v>
@@ -5125,10 +5192,10 @@
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5164,13 +5231,13 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5179,10 +5246,10 @@
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5211,22 +5278,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.358</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
         <v>80.09999999999999</v>
@@ -5235,37 +5302,37 @@
         <v>0.451</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M27" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.325</v>
+        <v>0.324</v>
       </c>
       <c r="O27" t="n">
         <v>22.7</v>
       </c>
       <c r="P27" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.773</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T27" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
         <v>6.3</v>
@@ -5280,22 +5347,22 @@
         <v>21.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT27" t="n">
         <v>8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5349,10 +5416,10 @@
         <v>28</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5396,13 +5463,13 @@
         <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.611</v>
+        <v>0.63</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,43 +5478,43 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K28" t="n">
         <v>0.455</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.36</v>
+        <v>0.364</v>
       </c>
       <c r="O28" t="n">
         <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.5</v>
       </c>
       <c r="V28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
@@ -5462,37 +5529,37 @@
         <v>19.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
         <v>100.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG28" t="n">
         <v>9</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>10</v>
       </c>
       <c r="AH28" t="n">
         <v>2</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,7 +5571,7 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5513,19 +5580,19 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,67 +5660,67 @@
         <v>38.4</v>
       </c>
       <c r="J29" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K29" t="n">
         <v>0.457</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M29" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" t="n">
         <v>25.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="O29" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>25.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0.783</v>
       </c>
       <c r="R29" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S29" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB29" t="n">
         <v>105.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -5674,16 +5741,16 @@
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5698,7 +5765,7 @@
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>22</v>
@@ -5710,7 +5777,7 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>18</v>
@@ -5722,13 +5789,13 @@
         <v>23</v>
       </c>
       <c r="BA29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.37</v>
+        <v>0.358</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,7 +5842,7 @@
         <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.45</v>
@@ -5784,40 +5851,40 @@
         <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.731</v>
+        <v>0.735</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S30" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T30" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
@@ -5826,25 +5893,25 @@
         <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB30" t="n">
         <v>95.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5859,16 +5926,16 @@
         <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5886,16 +5953,16 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW30" t="n">
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
@@ -5907,7 +5974,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
@@ -5939,43 +6006,43 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
         <v>33</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.611</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I31" t="n">
         <v>38.7</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M31" t="n">
         <v>16.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.369</v>
+        <v>0.374</v>
       </c>
       <c r="O31" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P31" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q31" t="n">
         <v>0.743</v>
@@ -5984,10 +6051,10 @@
         <v>10.5</v>
       </c>
       <c r="S31" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T31" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U31" t="n">
         <v>24.4</v>
@@ -6011,13 +6078,13 @@
         <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>11</v>
@@ -6026,7 +6093,7 @@
         <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>11</v>
@@ -6038,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6056,7 +6123,7 @@
         <v>21</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
@@ -6071,7 +6138,7 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
@@ -6080,19 +6147,19 @@
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-20-2014-15</t>
+          <t>2015-02-20</t>
         </is>
       </c>
     </row>
